--- a/output/review_report_sample_result.xlsx
+++ b/output/review_report_sample_result.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="サマリー" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keihi_seisan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nyuko_irai" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="report_sample" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="report_sample" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入稿依頼書" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -70,14 +70,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00EFEFEF"/>
+        <bgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEFEF"/>
-        <bgColor rgb="00EFEFEF"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -550,11 +550,11 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>nyuko_irai.docx</t>
+          <t>report_sample.md</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>2</v>
@@ -568,14 +568,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>report_sample.md</t>
+          <t>入稿依頼書.docx</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>レビュー日時： 2026-08-24 14:55</t>
+          <t>レビュー日時： 2026-08-25 09:05</t>
         </is>
       </c>
     </row>
@@ -659,17 +659,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">合計		</t>
+          <t>合計</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>合計行の金額欄が空欄になっています。各項目の金額の合計値（5,680）が計算・記載されていません。</t>
+          <t>合計行の金額欄が空欄になっています。各明細の合計値（5,680）が計算・記載されていません。</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>合計の金額欄に「5,680」と記入してください。</t>
+          <t>合計欄の金額に「5680」（または「5,680」）を入力してください。</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>金額</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>金額の単位（円など）が指定されておらず、また数値に3桁区切りのカンマが含まれていません。</t>
+          <t>金額に3桁区切りのカンマが付与されておらず、視認性に欠けています。</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>ヘッダー列を「金額（円）」と変更するか、各数値に「1,200」のように桁区切りカンマを記載してください。</t>
+          <t>「1,200」「3,500」のように、3桁区切りのカンマ表記（カンマ編集）に統一してください。</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -726,14 +726,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>対象ファイル： nyuko_irai.docx</t>
+          <t>対象ファイル： report_sample.md</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>レビュー日時： 2026-08-24 14:55</t>
+          <t>レビュー日時： 2026-08-25 09:05</t>
         </is>
       </c>
     </row>
@@ -775,17 +775,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>納品予定日：2026年2月30日</t>
+          <t>2026年13月度</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2026年2月30日は存在しない日付です（2026年2月は28日までしかありません）。</t>
+          <t>存在しない「13月」という月が指定されています。</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>正しい納品予定日（例：2026年2月27日や2026年3月2日など）に修正してください。</t>
+          <t>正しい月（例：「2026年1月度」や「2025年12月度」など）に修正してください。</t>
         </is>
       </c>
     </row>
@@ -800,17 +800,67 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>写真は5枚使用します。 / 使用画像枚数 | 3枚</t>
+          <t>来期は市場環境の悪化が見込まれるため、全社的に慎重な計画としております。なお、来期の売上目標は前期比150%の大幅増を予定しており、積極的な投資を行う方針です。</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>本文の記載（5枚）と表内の記載（3枚）で、使用する写真・画像の枚数が食い違っており矛盾しています。</t>
+          <t>「慎重な計画」としているのに対して、「前期比150%の大幅増」「積極的な投資を行う」と記載されており、文章の方針に矛盾が生じています。</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>正しい枚数を確認し、本文と表の記載を統一してください。</t>
+          <t>慎重な計画に合わせて目標値や投資方針を見直すか、あるいは積極投資に転じる根拠・理由を追加して整合性を持たせてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>## 来期の見通し</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>月次報告書であるにもかかわらず、見出しや本文で「来期」「前期比」といった期単位の表記が使われており、単位の表記ゆれ・不整合が生じています。</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>月次の報告に合わせて「来月の見通し」「前月比」などに修正するか、年度計画に関する記述であることを明記してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>よろしくおねがいします。</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>「おねがい」がひらがな表記になっており、ビジネス文書としての表記の一貫性を欠いています。</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>「よろしくお願いいたします。」または「よろしくお願いします。」と漢字表記に修正してください。</t>
         </is>
       </c>
     </row>
@@ -842,14 +892,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>対象ファイル： report_sample.md</t>
+          <t>対象ファイル： 入稿依頼書.docx</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>レビュー日時： 2026-08-24 14:55</t>
+          <t>レビュー日時： 2026-08-25 09:05</t>
         </is>
       </c>
     </row>
@@ -891,17 +941,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026年13月度</t>
+          <t>入港依頼書</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>存在しない月（13月）が記載されています。</t>
+          <t>タイトルにある「入港」は誤字である可能性が高いです。Webページ作成等の依頼内容から判断して「入稿」の誤りと思われます。</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>正しい対象月（例：2026年12月度、または2026年1月度など）に修正してください。</t>
+          <t>「入稿依頼書」へ修正してください。</t>
         </is>
       </c>
     </row>
@@ -916,17 +966,17 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>来期は市場環境の悪化が見込まれるため、全社的に慎重な計画としております。なお、来期の売上目標は前期比150%の大幅増を予定しており、積極的な投資を行う方針です。</t>
+          <t>2026年2月30日</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>前半で「慎重な計画」としているのに対し、直後で「売上目標150%大幅増」「積極的な投資」と記載されており、文章内で方針が食い違っています。</t>
+          <t>2026年2月30日は存在しない日付です（2026年2月は28日までです）。</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>市場環境悪化に伴う現実的な目標値に見直すか、積極投資を行う背景や整合性のある根拠・方針に文章を修正してください。</t>
+          <t>正しい納品予定日に修正してください。</t>
         </is>
       </c>
     </row>
@@ -934,24 +984,24 @@
       <c r="A7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>よろしくおねがいします。</t>
+          <t>写真は5枚使用します。 / 使用画像枚数 | 3枚</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>「おねがいします」がひらがな表記になっており、他の文章の丁寧な敬語表現（です・ます調）と比べて表記の一貫性を欠いています。</t>
+          <t>本文の「写真は5枚使用します」という記載と、表内の「使用画像枚数 | 3枚」という数値が一致しておらず矛盾しています。</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>「よろしくお願いいたします。」または「よろしくお願いします。」と漢字表記・適切な敬語表現に修正してください。</t>
+          <t>使用する画像の枚数を5枚または3枚のいずれかに統一してください。</t>
         </is>
       </c>
     </row>
